--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:39</t>
+    <t xml:space="preserve">2026-09-09 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:58</t>
+    <t xml:space="preserve">2026-09-18 17:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
@@ -30,42 +30,42 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Máfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Bueno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago Ranco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
-    <t xml:space="preserve">Corral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lago Ranco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Bueno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Unión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máfil</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:03</t>
+    <t xml:space="preserve">2026-09-27 21:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -495,13 +495,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>163129</v>
+        <v>7721</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>175117</v>
+        <v>7380</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>93.15</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5074</v>
+        <v>21142</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5444</v>
+        <v>20488</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>93.2</v>
+        <v>103.19</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>21835</v>
+        <v>18008</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>23016</v>
+        <v>17524</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>94.87</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="5">
@@ -537,13 +537,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10010</v>
+        <v>15514</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10281</v>
+        <v>15255</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>97.36</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="6">
@@ -551,13 +551,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>32395</v>
+        <v>39903</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32867</v>
+        <v>39446</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>98.56</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>20706</v>
+        <v>36256</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>20725</v>
+        <v>35870</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.91</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>36256</v>
+        <v>20706</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>35870</v>
+        <v>20725</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>101.08</v>
+        <v>99.91</v>
       </c>
     </row>
     <row r="9">
@@ -593,13 +593,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>39903</v>
+        <v>32395</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>39446</v>
+        <v>32867</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>101.16</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="10">
@@ -607,13 +607,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>15514</v>
+        <v>10010</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>15255</v>
+        <v>10281</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>101.7</v>
+        <v>97.36</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>18008</v>
+        <v>21835</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>17524</v>
+        <v>23016</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>102.76</v>
+        <v>94.87</v>
       </c>
     </row>
     <row r="12">
@@ -635,13 +635,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>21142</v>
+        <v>5074</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>20488</v>
+        <v>5444</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>103.19</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="13">
@@ -649,13 +649,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>7721</v>
+        <v>163129</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7380</v>
+        <v>175117</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>104.62</v>
+        <v>93.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_los_rios.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:46</t>
+    <t xml:space="preserve">2026-10-05 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
